--- a/95 Файлы/Допуск. М2/Допуск. М2. Интерлифт-Юг.xlsx
+++ b/95 Файлы/Допуск. М2/Допуск. М2. Интерлифт-Юг.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="87">
   <si>
     <t>Наименование объекта(ов):</t>
   </si>
@@ -263,14 +263,54 @@
     <t>Зеленский А.В.</t>
   </si>
   <si>
-    <t>с 1.04.2026 по 30.04.2026</t>
+    <t>с 1.05.2026 по 31.05.2026</t>
+  </si>
+  <si>
+    <t>Агеев</t>
+  </si>
+  <si>
+    <t>Андреевич</t>
+  </si>
+  <si>
+    <t>Мунасипов</t>
+  </si>
+  <si>
+    <t>Ильгиз</t>
+  </si>
+  <si>
+    <t>Маратович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пермский край, Бардымский     р-он, с. Сараши,  ул.М.Горкого д. 53
+</t>
+  </si>
+  <si>
+    <t>Ведущий инженер, Ремонтная служба, Группа по эксплуатации лифтового оборудования и грузоподъемных механизмов</t>
+  </si>
+  <si>
+    <t>Пермский край, Пермский район, деревня Нестюково</t>
+  </si>
+  <si>
+    <t>Р.Пос. Новоспасское, Новоспасского р-на Ульяновской обл.</t>
+  </si>
+  <si>
+    <t>Санкт-Петербург, ул. Адмирала Трибуца, д.7, кв. 137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Т035ЕА159 </t>
+  </si>
+  <si>
+    <t>Мунасипов И.М.</t>
+  </si>
+  <si>
+    <t>Лада 211440</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,6 +399,12 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -512,11 +558,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -594,9 +641,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -613,15 +657,87 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -631,91 +747,42 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
@@ -991,7 +1058,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD27"/>
+  <dimension ref="A1:AD30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" style="1" customWidth="1"/>
@@ -1018,131 +1085,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="42"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="56"/>
     </row>
     <row r="2" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45" t="s">
+      <c r="C2" s="49"/>
+      <c r="D2" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="46"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="49" t="s">
+      <c r="C4" s="49"/>
+      <c r="D4" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:30" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="47" t="s">
+      <c r="C5" s="49"/>
+      <c r="D5" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="48"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="47" t="s">
+      <c r="C6" s="49"/>
+      <c r="D6" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="48"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="51" t="s">
+      <c r="C7" s="49"/>
+      <c r="D7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="52"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="41"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="53"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="43"/>
     </row>
     <row r="9" spans="1:30" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="56"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="46"/>
     </row>
     <row r="10" spans="1:30" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
@@ -1166,16 +1233,16 @@
       <c r="H10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="57" t="s">
+      <c r="I10" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="58"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="30"/>
-      <c r="AD10" s="30"/>
+      <c r="J10" s="39"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="29"/>
+      <c r="AC10" s="29"/>
+      <c r="AD10" s="29"/>
     </row>
     <row r="11" spans="1:30" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1187,29 +1254,29 @@
       <c r="C11" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="29">
+      <c r="E11" s="27"/>
+      <c r="F11" s="28">
         <v>28424</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="31"/>
-      <c r="J11" s="32" t="s">
+      <c r="I11" s="30"/>
+      <c r="J11" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="30"/>
-      <c r="AD11" s="30"/>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="29"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="29"/>
     </row>
     <row r="12" spans="1:30" ht="63" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1246,9 +1313,9 @@
       <c r="Y12" s="21"/>
       <c r="Z12" s="21"/>
       <c r="AA12" s="22"/>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="30"/>
-      <c r="AD12" s="30"/>
+      <c r="AB12" s="29"/>
+      <c r="AC12" s="29"/>
+      <c r="AD12" s="29"/>
     </row>
     <row r="13" spans="1:30" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1264,13 +1331,13 @@
         <v>55</v>
       </c>
       <c r="E13" s="20"/>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <v>29317</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="27" t="s">
         <v>58</v>
       </c>
       <c r="I13" s="20"/>
@@ -1285,9 +1352,9 @@
       <c r="Y13" s="21"/>
       <c r="Z13" s="21"/>
       <c r="AA13" s="22"/>
-      <c r="AB13" s="30"/>
-      <c r="AC13" s="30"/>
-      <c r="AD13" s="30"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
     </row>
     <row r="14" spans="1:30" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1325,8 +1392,8 @@
       <c r="Z14" s="21"/>
       <c r="AA14" s="22"/>
       <c r="AB14" s="25"/>
-      <c r="AC14" s="30"/>
-      <c r="AD14" s="30"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
     </row>
     <row r="15" spans="1:30" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1364,230 +1431,330 @@
       <c r="Z15" s="21"/>
       <c r="AA15" s="22"/>
       <c r="AB15" s="25"/>
-      <c r="AC15" s="30"/>
-      <c r="AD15" s="30"/>
-    </row>
-    <row r="16" spans="1:30" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="60" t="s">
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+    </row>
+    <row r="16" spans="1:30" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>6</v>
+      </c>
+      <c r="B16" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="70"/>
+      <c r="F16" s="16">
+        <v>32142</v>
+      </c>
+      <c r="G16" s="71" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="71" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" s="70"/>
+      <c r="J16" s="71" t="s">
+        <v>80</v>
+      </c>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="21"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="29"/>
+      <c r="AD16" s="29"/>
+    </row>
+    <row r="17" spans="1:30" ht="126" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>7</v>
+      </c>
+      <c r="B17" s="65" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="63"/>
+      <c r="F17" s="67">
+        <v>33501</v>
+      </c>
+      <c r="G17" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="72" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="63"/>
+      <c r="J17" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="21"/>
+      <c r="Z17" s="21"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="29"/>
+      <c r="AD17" s="29"/>
+    </row>
+    <row r="18" spans="1:30" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="62"/>
-    </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="59" t="s">
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="36"/>
+    </row>
+    <row r="19" spans="1:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59" t="s">
+      <c r="C19" s="33"/>
+      <c r="D19" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59" t="s">
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="59"/>
-    </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="J19" s="33"/>
+    </row>
+    <row r="20" spans="1:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>1</v>
       </c>
-      <c r="B18" s="64" t="s">
+      <c r="B20" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="64" t="s">
+      <c r="C20" s="73"/>
+      <c r="D20" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="20" t="s">
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="70" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="21" spans="1:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>2</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B21" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63" t="s">
+      <c r="C21" s="38"/>
+      <c r="D21" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>3</v>
-      </c>
-      <c r="B20" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>4</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
       <c r="I21" s="26"/>
       <c r="J21" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>5</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
+        <v>3</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
       <c r="I22" s="26"/>
       <c r="J22" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>4</v>
+      </c>
       <c r="B23" s="37" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
+      <c r="D23" s="37" t="s">
+        <v>34</v>
+      </c>
       <c r="E23" s="37"/>
       <c r="F23" s="37"/>
       <c r="G23" s="37"/>
       <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-    </row>
-    <row r="24" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="38" t="s">
+      <c r="I23" s="26"/>
+      <c r="J23" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>5</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="68" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="68">
+        <v>6</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+    </row>
+    <row r="27" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="39" t="s">
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="35" t="s">
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+    </row>
+    <row r="28" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="36" t="s">
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-    </row>
-    <row r="26" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="3">
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+    </row>
+    <row r="29" spans="1:30" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="B7:C7"/>
+  <mergeCells count="37">
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:J3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:J6"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="H24:J24"/>
   </mergeCells>
   <pageMargins left="0.31388888888888899" right="0.31388888888888899" top="0.55000000000000004" bottom="0.55000000000000004" header="0.31388888888888899" footer="0.31388888888888899"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
